--- a/ui/public/sample/sample-datdai.xlsx
+++ b/ui/public/sample/sample-datdai.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vlute\kiemketaisan\ui\public\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{44957C59-4CEF-4CFB-8E44-FC69232DC024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF399E3E-E644-4F29-B888-2225DFF8FDCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{A3EABE27-5327-408F-BFBC-010F01E2E4AF}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Mã giấy chứng nhận quyền sở hữu</t>
   </si>
@@ -120,6 +120,12 @@
   </si>
   <si>
     <t>Số 1 Xuân Thủy, Phường Dịch Vọng Hậu, Cầu Giấy, Hà Nội</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>Thửa</t>
   </si>
 </sst>
 </file>
@@ -167,7 +173,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -186,8 +192,20 @@
         <bgColor theme="0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -225,11 +243,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -253,6 +297,30 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -587,7 +655,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5543B858-F816-42BF-955C-5C3B426D08EF}">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.36328125" bestFit="1" customWidth="1"/>
@@ -604,7 +672,7 @@
     <col min="14" max="14" width="54.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="75" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="75" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -641,14 +709,20 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="9" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="O1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
         <v>251436422887451</v>
       </c>
@@ -681,12 +755,14 @@
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="3" t="s">
+      <c r="M2" s="10"/>
+      <c r="N2" s="17" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="O2" s="18"/>
+      <c r="P2" s="18"/>
+    </row>
+    <row r="3" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
       <c r="B3" s="7"/>
       <c r="C3" s="6"/>
@@ -699,10 +775,12 @@
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="M3" s="11"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+    </row>
+    <row r="4" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
       <c r="B4" s="7"/>
       <c r="C4" s="6"/>
@@ -715,10 +793,12 @@
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="M4" s="11"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+    </row>
+    <row r="5" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="6"/>
       <c r="B5" s="7"/>
       <c r="C5" s="6"/>
@@ -731,10 +811,12 @@
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="M5" s="11"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+    </row>
+    <row r="6" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="6"/>
       <c r="B6" s="7"/>
       <c r="C6" s="6"/>
@@ -747,10 +829,12 @@
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-    </row>
-    <row r="7" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="M6" s="11"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+    </row>
+    <row r="7" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="6"/>
       <c r="B7" s="7"/>
       <c r="C7" s="6"/>
@@ -763,10 +847,12 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="6"/>
-    </row>
-    <row r="8" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="M7" s="11"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+    </row>
+    <row r="8" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="8"/>
       <c r="B8" s="6"/>
       <c r="C8" s="8"/>
@@ -779,10 +865,12 @@
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="8"/>
-    </row>
-    <row r="9" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="M8" s="12"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+    </row>
+    <row r="9" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="6"/>
       <c r="B9" s="7"/>
       <c r="C9" s="6"/>
@@ -795,10 +883,12 @@
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="M9" s="11"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+    </row>
+    <row r="10" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="6"/>
       <c r="B10" s="7"/>
       <c r="C10" s="6"/>
@@ -811,10 +901,12 @@
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="6"/>
-    </row>
-    <row r="11" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="M10" s="11"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+    </row>
+    <row r="11" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="6"/>
       <c r="B11" s="7"/>
       <c r="C11" s="6"/>
@@ -827,10 +919,12 @@
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="12" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="M11" s="11"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="13"/>
+    </row>
+    <row r="12" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="6"/>
       <c r="B12" s="7"/>
       <c r="C12" s="6"/>
@@ -843,10 +937,12 @@
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="6"/>
-    </row>
-    <row r="13" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="M12" s="11"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="13"/>
+    </row>
+    <row r="13" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="6"/>
       <c r="B13" s="7"/>
       <c r="C13" s="6"/>
@@ -859,10 +955,12 @@
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="6"/>
-    </row>
-    <row r="14" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="M13" s="11"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="13"/>
+    </row>
+    <row r="14" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="6"/>
       <c r="B14" s="7"/>
       <c r="C14" s="6"/>
@@ -875,8 +973,10 @@
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="6"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
